--- a/public/Participants_QR_Complet.xlsx
+++ b/public/Participants_QR_Complet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenove\participants-app\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CE6555C-20E5-4E97-8959-29456B7FDA49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2263F84C-7844-4B29-8D54-6F622A2FA3D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5165,7 +5165,7 @@
     <col min="4" max="4" width="47.44140625" customWidth="1"/>
     <col min="5" max="5" width="41.33203125" customWidth="1"/>
     <col min="6" max="6" width="28.6640625" customWidth="1"/>
-    <col min="7" max="7" width="15" customWidth="1"/>
+    <col min="7" max="7" width="28.21875" customWidth="1"/>
     <col min="9" max="9" width="16.88671875" customWidth="1"/>
     <col min="10" max="10" width="13.33203125" customWidth="1"/>
   </cols>
